--- a/data/stuff_ongoing.xlsx
+++ b/data/stuff_ongoing.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,6 +439,11 @@
           <t>재고현황</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>카테고리</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -449,6 +454,11 @@
       <c r="B2" t="n">
         <v>8</v>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>반납물품</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -459,6 +469,11 @@
       <c r="B3" t="n">
         <v>5</v>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>반납물품</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -467,7 +482,12 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-1</v>
+        <v>4</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>반납물품</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -477,7 +497,12 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1</v>
+        <v>5</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>반납물품</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -489,6 +514,11 @@
       <c r="B6" t="n">
         <v>2</v>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>반납물품</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -497,7 +527,12 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1</v>
+        <v>4</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>반납물품</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -507,7 +542,12 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1</v>
+        <v>5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>반납물품</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -517,7 +557,12 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-1</v>
+        <v>4</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>반납물품</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -527,7 +572,12 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-1</v>
+        <v>5</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>반납물품</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -537,7 +587,12 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>반납물품</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -547,7 +602,12 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-1</v>
+        <v>5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>반납물품</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -557,7 +617,12 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-1</v>
+        <v>4</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>일회용품</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -567,7 +632,12 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-1</v>
+        <v>4</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>일회용품</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -577,7 +647,12 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-1</v>
+        <v>5</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>반납물품</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -587,7 +662,12 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-1</v>
+        <v>5</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>일회용품</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -597,7 +677,12 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-1</v>
+        <v>5</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>일회용품</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -607,7 +692,12 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-1</v>
+        <v>5</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>일회용품</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -617,7 +707,12 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-1</v>
+        <v>4</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>일회용품</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -627,17 +722,12 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>test stuff</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>32</v>
+        <v>4</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>일회용품</t>
+        </is>
       </c>
     </row>
   </sheetData>
